--- a/AAII_Financials/Quarterly/DHI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DHI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
   <si>
     <t>DHI</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9227100</v>
+      </c>
+      <c r="E8" s="3">
         <v>7558100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6886900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9677800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9225700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7734000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7613000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10002600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9965700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9107200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7726000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10504000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9725600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7972900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7257800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9639400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8788100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7999000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7053400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8109300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7284600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6446900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5933400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6400300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5390000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4500000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4020700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5038900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4906300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4128700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3519000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4505100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4435300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3794700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3332700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4159100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3776400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3251300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2904200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3741200</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7059000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5822700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5281000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7523800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6962300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5803800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5686200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7403900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7308900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6760700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5713700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7662600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7131000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5972400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5271900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6723200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5869800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5420100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4901800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5694300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5207700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4647700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4324600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4747900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4079800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3442000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3080700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3869300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3812400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3242900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2743100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3451500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3388300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2931500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2576400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3243600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2955700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2547100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2265600</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2914300</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2017700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1594300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1479300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2011500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2116900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1790300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1793100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2452600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2505800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2198900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1885700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2707300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2460200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1869700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1985900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2916200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2918300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2578900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2151600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2415000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2076900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1799200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1608800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1652400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1310200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1058000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>940000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1169600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1093900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>885800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>775900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1053600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1047000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>863200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>756300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>915500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>820700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>704200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>638600</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>826900</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,175 +1496,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E14" s="3">
         <v>32100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>11200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>57300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>54200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>30000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>16600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>44400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>14800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>18100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>10800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>23800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>20300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>38800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>10600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>4900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>10000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>24000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>4100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>9000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>6800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>6100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>10100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>4800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>12700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>19700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>14300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>8500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>7600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>35600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>15300</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>20300</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>5400</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>2800</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>2300</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E15" s="3">
         <v>28100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>27700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>27400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>25200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>24600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>23600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>22400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>20000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>21400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>23700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>26700</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8028500</v>
+      </c>
+      <c r="E17" s="3">
         <v>6707300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6127700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8471200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7882100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6682100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6543800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8338500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8205500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7617700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6523800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8523700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7962800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6729900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5990600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7573600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6604800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6115700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5556100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6382800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5869000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5267000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4899100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5344200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4607600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3878700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3497400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4378800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4279600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3665900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3143300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3897400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3819100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3349900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2941500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3673500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3331900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2897400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2586100</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3308100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1198600</v>
+      </c>
+      <c r="E18" s="3">
         <v>850800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>759200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1206600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1343600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1051900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1069200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1664100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1760200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1489500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1202200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1980300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1762800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1243000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1267200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2065800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2183300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1883300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1497300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1726500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1415600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1179900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1034300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1056100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>782400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>621300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>523300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>660100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>626700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>462800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>375700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>607700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>616200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>444800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>391200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>485600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>444500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>353900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>318100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>433100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,53 +2085,54 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-49500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-48700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-50100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-55500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-68700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-45200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-57300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-90000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-53600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-52600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-51400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-56100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-31900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-26100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -2174,130 +2208,136 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1277100</v>
+      </c>
+      <c r="E21" s="3">
         <v>927600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>837000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1289500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1437500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1121700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1150600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1777700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1836200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1563200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1273600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2057800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1818400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1295800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1287000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2087000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2204200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1903200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1516700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1743700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1433000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1198800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1054700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1079100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>801000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>641100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>542300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>679700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>645000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>480000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>392600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>623500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>629700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>461700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>407400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>499900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>457600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>366800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>332500</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>452700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2340,8 +2380,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1226200</v>
+      </c>
+      <c r="E23" s="3">
         <v>867400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>798100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1204800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1358100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1067100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1109900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1709700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1799000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1528500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1247500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2018300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1783900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1245300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1267200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2065800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2183300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1883300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1497300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1726500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1415600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1179900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1034300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1056100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>782400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>621300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>523300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>660100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>626700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>462800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>375700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>607700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>616200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>444800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>391200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>485600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>444500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>353900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>318100</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>433100</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>307500</v>
+      </c>
+      <c r="E24" s="3">
         <v>209400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>196700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>288000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>325000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>248000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>258000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>409900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>432200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>344800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>291800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>492800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>432200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>295700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>298900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>417600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>524000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>441000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>351500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>381000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>299100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>246000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>239100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>224900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>149500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>137300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>90800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>156200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>153100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>108400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>89000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>138800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>162500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>94000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>93700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>172300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>155500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>124700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>111200</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>149400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>918700</v>
+      </c>
+      <c r="E26" s="3">
         <v>658000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>601400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>916800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1033100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>819100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>851900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1299800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1366800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1183700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>955700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1525500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1351700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>949600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>968300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1648200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1659300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1442300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1145800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1345500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1116500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>933900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>795200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>831200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>632900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>484000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>432500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>503900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>473600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>354400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>286700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>468900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>453700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>350800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>297500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>313300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>289000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>229200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>206900</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>283700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>904900</v>
+      </c>
+      <c r="E27" s="3">
         <v>647900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>594800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>905300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1024600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>810400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>844900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1283400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1353600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1172100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>947400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1509700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1335100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>942200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>958700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1631800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1647800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1436300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1141600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1339000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1115500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>929500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>791800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>829000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>630700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>482700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>431300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>505300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>474800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>351300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>287200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>466200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>453800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>351000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>298000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>313300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>289000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>229200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>206900</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>283700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3236,8 +3297,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3245,8 +3306,8 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI29" s="3">
         <v>0</v>
@@ -3255,10 +3316,10 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-108700</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,53 +3583,56 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>49500</v>
+      </c>
+      <c r="E32" s="3">
         <v>48700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>50100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>55500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>68700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>45200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>57300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>90000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>53600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>52600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>51400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>56100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>31900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>26100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3638,130 +3708,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>904900</v>
+      </c>
+      <c r="E33" s="3">
         <v>647900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>594800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>905300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1024600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>810400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>844900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1283400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1353600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1172100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>947400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1509700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1335100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>942200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>958700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1631800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1647800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1436300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1141600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1339000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1115500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>929500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>791800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>829000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>630700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>482700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>431300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>505300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>474800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>351300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>287200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>466200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>453800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>351000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>189300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>313300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>289000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>229200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>206900</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>283700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>904900</v>
+      </c>
+      <c r="E35" s="3">
         <v>647900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>594800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>905300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1024600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>810400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>844900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1283400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1353600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1172100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>947400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1509700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1335100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>942200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>958700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1631800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1647800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1436300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1141600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1339000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1115500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>929500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>791800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>829000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>630700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>482700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>431300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>505300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>474800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>351300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>287200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>466200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>453800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>351000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>189300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>313300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>289000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>229200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>206900</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>283700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2078700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1917900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2506300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2985400</v>
       </c>
-      <c r="G41" s="3">
-        <v>2346000</v>
-      </c>
       <c r="H41" s="3">
+        <v>2614000</v>
+      </c>
+      <c r="I41" s="3">
         <v>2202300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3050100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4516400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2686600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2747900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3096500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3684500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3126100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2765600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2591100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2540500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1655700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1663900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2442100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3210400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1942700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2205200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2454900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3018500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2353500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1522800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1583300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1494300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>864200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>698800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>737000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1473100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1178200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1010800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>920300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1042600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>512400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>993200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1150300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1303200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,419 +4553,431 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>283200</v>
+      </c>
+      <c r="E43" s="3">
         <v>296500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>307200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>331000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>291400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>349600</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="J43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>303900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>320100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>323800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>295400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>333000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>315900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>282300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>318000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>348800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>294900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>263500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>261300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>263100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>250400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>257100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>227800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>224300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>212600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>189000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>171800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>178700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>177300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>136300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>131000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>136300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>139800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>147000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>153000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>134400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>39400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>31800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>31000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>26686900</v>
+      </c>
+      <c r="E44" s="3">
         <v>26303800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>25606000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>25287300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>26726100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>26482400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>26080500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>24903200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>25536100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>24840000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>24050300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>22373300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>22983500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>22571700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>22445300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>21655700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>21698900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>19846500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>18202500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>16479100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>16011700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>14476300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>13576500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>12237400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>12138700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>12224500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>11899200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>11282000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>11702300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>11920300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>11595600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>10395000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>10303300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>10144400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>10040200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>9237100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>9554000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>9038100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>8742400</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>8340900</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3141100</v>
+      </c>
+      <c r="E45" s="3">
         <v>3090200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3003200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2995800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2721900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2691000</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2603800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2476300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2304500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2452000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2332800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2187000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2014400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>88100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>77400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>93100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>77200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>70400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>51600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>54700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>51700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>53400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>46000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>35000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>48400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>58600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>49600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>33900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>30900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>36400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>36900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>19000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>23300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>32200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>30800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>12000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>19500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>24000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>35503300</v>
+      </c>
+      <c r="E46" s="3">
         <v>34627300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>33650700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>34476300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>35405800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>34738500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>30943900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>35067800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>34138500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>33436100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32385100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>31646000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31452400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>30227400</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,296 +5053,305 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E47" s="3">
         <v>15500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>22600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>42700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>62400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>52700</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>44500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>39900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>46300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>81100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>19800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>58800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1858500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2460300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2151600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2307600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1894100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2085900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1698700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1806900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1488000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1576100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1547500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1421600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1065800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1117800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>991200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>830900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>655600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>807400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>712100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>690300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>624300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>587300</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>710000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>662900</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>633000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>742700</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>670800</v>
+      </c>
+      <c r="E48" s="3">
         <v>656000</v>
       </c>
-      <c r="E48" s="3">
-        <v>644100</v>
-      </c>
       <c r="F48" s="3">
+        <v>648200</v>
+      </c>
+      <c r="G48" s="3">
         <v>637600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>606100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>581500</v>
       </c>
-      <c r="I48" s="3">
-        <v>520300</v>
-      </c>
       <c r="J48" s="3">
+        <v>524200</v>
+      </c>
+      <c r="K48" s="3">
         <v>578400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>567500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>522500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>514500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>487900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>465800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>549000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>548300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>518200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>524000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>475700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>448500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>428500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>402000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>928900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>781800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>718400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>667400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>627500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>599600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>462200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>454200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>437900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>391100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>401100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>385200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>380400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>357700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>455600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>282800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>248100</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>218400</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>251300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>199300</v>
+      </c>
+      <c r="E49" s="3">
         <v>183600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>211700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>190600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>183300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>168800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>163500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>169400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>168500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>166300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>181500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>174600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>184400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>168100</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>163500</v>
       </c>
       <c r="R49" s="3">
         <v>163500</v>
@@ -5288,10 +5399,10 @@
         <v>163500</v>
       </c>
       <c r="AG49" s="3">
+        <v>163500</v>
+      </c>
+      <c r="AH49" s="3">
         <v>158400</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>109200</v>
       </c>
       <c r="AI49" s="3">
         <v>109200</v>
@@ -5300,10 +5411,10 @@
         <v>109200</v>
       </c>
       <c r="AK49" s="3">
+        <v>109200</v>
+      </c>
+      <c r="AL49" s="3">
         <v>100000</v>
-      </c>
-      <c r="AL49" s="3">
-        <v>80000</v>
       </c>
       <c r="AM49" s="3">
         <v>80000</v>
@@ -5317,8 +5428,11 @@
       <c r="AP49" s="3">
         <v>80000</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>80000</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>105300</v>
+      </c>
+      <c r="E52" s="3">
         <v>80300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>81400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>75200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>67800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>70100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3129700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>72700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>76600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>56600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>39200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>80300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>75000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>51200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>159300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>173500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>186000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>156900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>160100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>182100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>173500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>169500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>162000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>166500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>177800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>164000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>166700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>211700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>195000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>204300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>256300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>226900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>263300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>275300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>292800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>381500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>394600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>462700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>476600</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>485800</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36511300</v>
+      </c>
+      <c r="E54" s="3">
         <v>35566900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>34639600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>35471200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36395900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>35690000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>35029700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36104300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>35151400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>34398200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33381600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32582400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32323100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31170800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>30264500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>30351100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>28869900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26685300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>24999400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>24015900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>21793500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>21083800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>19780400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>18912300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17973900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17130000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>16322900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>15606600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>15224000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>15007000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>14535800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>14114600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>13593400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>13218100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12957300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>12184600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>11977100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>11921100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>11712100</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>11558900</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,419 +6145,429 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1388400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1323500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1026000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1221900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1388800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1373800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1372600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1345500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1412700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1386500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1260300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1246200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1369500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1251300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1205000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1360300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1507300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1378600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1150700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1177000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1250900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1137400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>845600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>900500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>761200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>707000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>659300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>634000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>681200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>658500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>697200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>624700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>655300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>582700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>575700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>637100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>656300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>580900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>545100</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>577500</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2087200</v>
+        <v>2416900</v>
       </c>
       <c r="E58" s="3">
+        <v>3202200</v>
+      </c>
+      <c r="F58" s="3">
         <v>2188100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2071400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2264500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1989500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1300100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2841800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2211700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3369200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2899600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1719200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2702800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2604100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2095200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2473400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1843600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2014900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1765800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1924100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1523100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1628800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1383500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1599100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1617000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1622300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1895700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1605300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>796500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>690700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>973800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>637700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>526300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>489800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>387500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>420000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>473400</v>
-      </c>
-      <c r="AN58" s="3">
-        <v>419000</v>
       </c>
       <c r="AO58" s="3">
         <v>419000</v>
       </c>
       <c r="AP58" s="3">
+        <v>419000</v>
+      </c>
+      <c r="AQ58" s="3">
         <v>473000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>866200</v>
+      </c>
+      <c r="E59" s="3">
         <v>848500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>990500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>836600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>618700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>557300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>862100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>594600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>631800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>612600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1049100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>865100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>688400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>811300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2681100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2771700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2745900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2283700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2435200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2108200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1882500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1979400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1744400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1471900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1452900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1206300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1278700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1183100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1157400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1099800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1104000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1054200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>986400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>939900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>980200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>898000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>922100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>862400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>934100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>878500</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5436000</v>
+        <v>5906700</v>
       </c>
       <c r="E60" s="3">
+        <v>6551000</v>
+      </c>
+      <c r="F60" s="3">
         <v>5314400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5369100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5425300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5006400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4573200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5915200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5263000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6361100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6113300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4817900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5667100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5548400</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,175 +6643,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4556200</v>
+        <v>4771000</v>
       </c>
       <c r="E61" s="3">
+        <v>3441200</v>
+      </c>
+      <c r="F61" s="3">
         <v>3428100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3993800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5097900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4622800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3863900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3192200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3551100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2616600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2605900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3473000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3465400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3431700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3595100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3593500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4131600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3555100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3489500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3488300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2893200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2843500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2842100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2684200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2680300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2684300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1887600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1794100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2654100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2931700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2368500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2565800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2567300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2744100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2870600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2451600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2453100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2803400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2798600</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2798300</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1383700</v>
+      </c>
+      <c r="E62" s="3">
         <v>1367300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1341700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1366100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1279700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1202100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1129700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1172500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1186600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1124100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1058900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1153600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1108300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1068900</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6747,8 +6893,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12104800</v>
+      </c>
+      <c r="E66" s="3">
         <v>11367900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10084200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10729000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11802900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10831300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9566800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10279900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10000700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10101800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9778100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9444500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10240800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10049000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10111200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10954800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10807400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9910400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9321700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9129400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7990600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8120700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7295200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7072300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6925900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6672000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6095500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5585700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5581600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5646700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5411100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5130200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4996100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5019200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5075300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4437500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4540900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>4701500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>4730800</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>4766400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>32800700</v>
+      </c>
+      <c r="E72" s="3">
         <v>32022900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>31504700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>31041400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>30254500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>29352300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>28667400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>27951000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>26765300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>25510200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>24437300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>23589800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>22164400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20914500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>20057900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>19185300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17631600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>16063000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14705800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13644300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12376900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>11333500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>10476700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9757800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8992500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8425400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>8006800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>7640100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>7190400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6771600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6476200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6217900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5798800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5392100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5088200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4946000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4670100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4418600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4226800</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4057200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23819500</v>
+      </c>
+      <c r="E76" s="3">
         <v>23625800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23995500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>24190400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>24052900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24327100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24943900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25312800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24656500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23815500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23153400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22696200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21656400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20712700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20153300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19396300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18062500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16774900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15677700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14886500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13802900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12963100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12485200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11840000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11048000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10458000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10227400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10020900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9642400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9360300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>9124700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8984400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8597300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>8198900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>7882000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>7747100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>7436200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>7219600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>6981300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>6792500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>904900</v>
+      </c>
+      <c r="E81" s="3">
         <v>647900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>594800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>905300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1024600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>810400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>844900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1283400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1353600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1172100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>947400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1509700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1335100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>942200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>958700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1631800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1647800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1436300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1141600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1339000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1115500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>929500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>791800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>829000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>630700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>482700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>431300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>505300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>474800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>351300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>287200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>466200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>453800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>351000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>189300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>313300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>289000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>229200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>206900</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>283700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E83" s="3">
         <v>24600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>24100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>23600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>22400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>21100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>20000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>26700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>19800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>21200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>19900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>19800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>21200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>20900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>19900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>19400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>17200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>17400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>18900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>20400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>23000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>18600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>19800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>19000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>19600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>18300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>17200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>16900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>15800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>13500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>16900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>16200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>14300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>13100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>12900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>14400</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>439300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-412500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>854000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2471800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>738600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-436200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>646700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1961600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>698300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-316700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-153400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2043000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>787500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>644500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>829100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1124600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>271800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-660500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-174100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>568900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>120400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>97200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-252100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>832700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>984000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-281300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-113800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>811400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>542400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-88600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-373100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>238700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>405300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-23800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-75000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>631000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-55100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-107500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-28200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>529400</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-37200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-27400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-43800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-46000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-34300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-32000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-62000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-23700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-47600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-40300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-29100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-47500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-40200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-35500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-41600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-30900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-47500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-15500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-14200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-16300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-29700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-19200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-21600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-40600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-28000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-16900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-11400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-14100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-14500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-59900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>48900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-70600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-44400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-53100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-44200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-116200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-45200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-29000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-37400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-57100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-95100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-39300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-127900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-37700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-142900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-42000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-304200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-42200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-26500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-45300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-104700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-91400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-65700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-65800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-16800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-17800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-67700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-310400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>11500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-23900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>153500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-161000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-47600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-42100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-31300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-85400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>127100</v>
+      </c>
+      <c r="E96" s="3">
         <v>129700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>131500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>118400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>122400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>125500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>128500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>97700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>98400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>99200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>99900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>84300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>85200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>85600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-86100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-78100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-79200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-79100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-80100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-71600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-72100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-72700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-72900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-63700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-63600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-64100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-64600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-55500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-56000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-55900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-56000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-47100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-47200</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-47100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-47000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-37400</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-37500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-37400</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-37300</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-29800</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-225500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-122100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1218100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2058200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-562800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-77300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2064600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-408100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-676600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>92200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-362800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1549200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-326200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-144700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-646600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-194000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>27600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-72800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-572000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>744500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-372400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-235500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-221700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-99600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-82800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>239500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>213500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-115000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-383100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>62200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-54200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>18900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-210700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-76400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>185700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-80500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-383200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-88300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-47600</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>160700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-578800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-480300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>368400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>146800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-550900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1475000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1524000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-73400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-251200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-555500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>492100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>333400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>462100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>39600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>888600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-775500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-772600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1268100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-262800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-243000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-565200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>667400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>835400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-58600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>81900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>628700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>154100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-37100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-737700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>269100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>170700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>53300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-50300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>495400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-480800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-157100</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-152900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>396400</v>
       </c>
     </row>
